--- a/data-raw/workbooks/kelpbio-3-bad-weight-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-3-bad-weight-nereo.xlsx
@@ -10,13 +10,14 @@
     <sheet name="density" sheetId="1" r:id="rId1"/>
     <sheet name="size" sheetId="2" r:id="rId2"/>
     <sheet name="weight" sheetId="3" r:id="rId3"/>
+    <sheet name="carbon" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="19">
   <si>
     <t>site</t>
   </si>
@@ -67,6 +68,12 @@
   </si>
   <si>
     <t>weight_kg</t>
+  </si>
+  <si>
+    <t>sample_mass_mg</t>
+  </si>
+  <si>
+    <t>carbon_mass_ug</t>
   </si>
 </sst>
 </file>
@@ -17491,4 +17498,502 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>2.49</v>
+      </c>
+      <c r="B2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2.15</v>
+      </c>
+      <c r="B3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2.51</v>
+      </c>
+      <c r="B4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>2.14</v>
+      </c>
+      <c r="B5">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>2.71</v>
+      </c>
+      <c r="B6">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>2.89</v>
+      </c>
+      <c r="B7">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>2.05</v>
+      </c>
+      <c r="B8">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>2.58</v>
+      </c>
+      <c r="B9">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>2.27</v>
+      </c>
+      <c r="B10">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>2.93</v>
+      </c>
+      <c r="B11">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>2.83</v>
+      </c>
+      <c r="B12">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>2.54</v>
+      </c>
+      <c r="B13">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>2.52</v>
+      </c>
+      <c r="B14">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>2.37</v>
+      </c>
+      <c r="B15">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>2.02</v>
+      </c>
+      <c r="B16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>2.2</v>
+      </c>
+      <c r="B17">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>2.61</v>
+      </c>
+      <c r="B18">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>2.13</v>
+      </c>
+      <c r="B19">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>2.03</v>
+      </c>
+      <c r="B20">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>2.4</v>
+      </c>
+      <c r="B21">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>2.44</v>
+      </c>
+      <c r="B22">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>2.87</v>
+      </c>
+      <c r="B23">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>2.45</v>
+      </c>
+      <c r="B24">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>2.88</v>
+      </c>
+      <c r="B25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>2.92</v>
+      </c>
+      <c r="B26">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>2.64</v>
+      </c>
+      <c r="B27">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>2.15</v>
+      </c>
+      <c r="B28">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>2.41</v>
+      </c>
+      <c r="B29">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>2.79</v>
+      </c>
+      <c r="B30">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>2.29</v>
+      </c>
+      <c r="B31">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>2.83</v>
+      </c>
+      <c r="B32">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>2.04</v>
+      </c>
+      <c r="B33">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>2.74</v>
+      </c>
+      <c r="B34">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>2.73</v>
+      </c>
+      <c r="B35">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>2.96</v>
+      </c>
+      <c r="B36">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>2.48</v>
+      </c>
+      <c r="B37">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>2.88</v>
+      </c>
+      <c r="B38">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>2.09</v>
+      </c>
+      <c r="B39">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>2.93</v>
+      </c>
+      <c r="B40">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>2.78</v>
+      </c>
+      <c r="B41">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>2.1</v>
+      </c>
+      <c r="B42">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>2.5</v>
+      </c>
+      <c r="B43">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>2.49</v>
+      </c>
+      <c r="B44">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>2.81</v>
+      </c>
+      <c r="B45">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>2.69</v>
+      </c>
+      <c r="B46">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>2.41</v>
+      </c>
+      <c r="B47">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>2.05</v>
+      </c>
+      <c r="B48">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>2.75</v>
+      </c>
+      <c r="B49">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>2.2</v>
+      </c>
+      <c r="B50">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>2.95</v>
+      </c>
+      <c r="B51">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>2.41</v>
+      </c>
+      <c r="B52">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>2.42</v>
+      </c>
+      <c r="B53">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>2.49</v>
+      </c>
+      <c r="B54">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>2.31</v>
+      </c>
+      <c r="B55">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>2.82</v>
+      </c>
+      <c r="B56">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>2.79</v>
+      </c>
+      <c r="B57">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>2.92</v>
+      </c>
+      <c r="B58">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>2.04</v>
+      </c>
+      <c r="B59">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>2.52</v>
+      </c>
+      <c r="B60">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>2.22</v>
+      </c>
+      <c r="B61">
+        <v>653</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>